--- a/testdata/result/누적강우 20년이후/2025 6061번 강우사상_누적강우20.xlsx
+++ b/testdata/result/누적강우 20년이후/2025 6061번 강우사상_누적강우20.xlsx
@@ -561,10 +561,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45882.96527777778</v>
+        <v>45854.46527777778</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -582,25 +582,25 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>0.74</v>
       </c>
       <c r="K2" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="L2" t="n">
-        <v>12.31</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="n">
-        <v>41.49</v>
+        <v>7.59</v>
       </c>
       <c r="N2" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -608,33 +608,33 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0.914638340473175</v>
+        <v>0.7551305294036865</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006018176209181547</v>
+        <v>0.02456584572792053</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06159747391939163</v>
+        <v>0.1310870200395584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07757690512763156</v>
+        <v>0.1567349537528899</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9006410837173462</v>
+        <v>0.9196199178695679</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03448737785220146</v>
+        <v>0.03711839392781258</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1452171057462692</v>
+        <v>0.1665867418050766</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1857077754220363</v>
+        <v>0.1926613451832323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45882.97222222222</v>
+        <v>45854.47222222222</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -661,19 +661,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="L3" t="n">
-        <v>11.88</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
-        <v>40.68</v>
+        <v>7.59</v>
       </c>
       <c r="N3" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45882.97916666666</v>
+        <v>45854.47916666666</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -718,19 +718,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>0.75</v>
       </c>
       <c r="K4" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
-        <v>11.06</v>
+        <v>2.75</v>
       </c>
       <c r="M4" t="n">
-        <v>39.87</v>
+        <v>7.59</v>
       </c>
       <c r="N4" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45882.98611111111</v>
+        <v>45854.48611111111</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -775,19 +775,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="K5" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="L5" t="n">
-        <v>10.66</v>
+        <v>2.98</v>
       </c>
       <c r="M5" t="n">
-        <v>39.07</v>
+        <v>7.59</v>
       </c>
       <c r="N5" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45882.99305555555</v>
+        <v>45854.49305555555</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -832,19 +832,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="K6" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>10.26</v>
+        <v>3.22</v>
       </c>
       <c r="M6" t="n">
-        <v>39.07</v>
+        <v>7.59</v>
       </c>
       <c r="N6" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45883</v>
+        <v>45854.5</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -889,19 +889,19 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>9.869999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="M7" t="n">
-        <v>38.28</v>
+        <v>7.59</v>
       </c>
       <c r="N7" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45883.00694444445</v>
+        <v>45854.50694444445</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -946,19 +946,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="K8" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
-        <v>9.869999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="M8" t="n">
-        <v>37.5</v>
+        <v>7.59</v>
       </c>
       <c r="N8" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45883.01388888889</v>
+        <v>45854.51388888889</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -1003,19 +1003,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="K9" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>9.48</v>
+        <v>3.46</v>
       </c>
       <c r="M9" t="n">
-        <v>36.72</v>
+        <v>7.59</v>
       </c>
       <c r="N9" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45883.02083333334</v>
+        <v>45854.52083333334</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="K10" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>9.109999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="M10" t="n">
-        <v>35.94</v>
+        <v>7.59</v>
       </c>
       <c r="N10" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45883.02777777778</v>
+        <v>45854.52777777778</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -1117,19 +1117,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="K11" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>9.109999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="M11" t="n">
-        <v>35.17</v>
+        <v>7.59</v>
       </c>
       <c r="N11" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45883.03472222222</v>
+        <v>45854.53472222222</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1168,28 +1168,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="J12" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="K12" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="L12" t="n">
-        <v>8.73</v>
+        <v>3.72</v>
       </c>
       <c r="M12" t="n">
-        <v>34.41</v>
+        <v>7.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0.161</v>
+        <v>0.074</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45883.04166666666</v>
+        <v>45854.54166666666</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1225,28 +1225,28 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.95</v>
+        <v>0.79</v>
       </c>
       <c r="K13" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="L13" t="n">
-        <v>8.73</v>
+        <v>3.72</v>
       </c>
       <c r="M13" t="n">
-        <v>33.66</v>
+        <v>7.59</v>
       </c>
       <c r="N13" t="n">
-        <v>0.161</v>
+        <v>0.09</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45883.04861111111</v>
+        <v>45854.54861111111</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="K14" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="L14" t="n">
-        <v>8.369999999999999</v>
+        <v>3.72</v>
       </c>
       <c r="M14" t="n">
-        <v>32.91</v>
+        <v>7.59</v>
       </c>
       <c r="N14" t="n">
-        <v>0.235</v>
+        <v>0.09</v>
       </c>
       <c r="O14" t="n">
         <v>0.488</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45883.05555555555</v>
+        <v>45854.55555555555</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1330,37 +1330,37 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.074</v>
+        <v>0.125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.488</v>
+        <v>0.451</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="K15" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="L15" t="n">
-        <v>8.369999999999999</v>
+        <v>3.72</v>
       </c>
       <c r="M15" t="n">
-        <v>32.17</v>
+        <v>7.59</v>
       </c>
       <c r="N15" t="n">
-        <v>0.309</v>
+        <v>0.215</v>
       </c>
       <c r="O15" t="n">
-        <v>0.976</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45883.0625</v>
+        <v>45854.5625</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1393,31 +1393,31 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.016</v>
+        <v>0.251</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="K16" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="L16" t="n">
-        <v>8.369999999999999</v>
+        <v>3.72</v>
       </c>
       <c r="M16" t="n">
-        <v>32.17</v>
+        <v>7.59</v>
       </c>
       <c r="N16" t="n">
-        <v>0.325</v>
+        <v>0.466</v>
       </c>
       <c r="O16" t="n">
-        <v>0.976</v>
+        <v>1</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1432,19 +1432,19 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45883.06944444445</v>
+        <v>45854.56944444445</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1453,28 +1453,28 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.463</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.488</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="K17" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="L17" t="n">
-        <v>8.01</v>
+        <v>3.72</v>
       </c>
       <c r="M17" t="n">
-        <v>31.44</v>
+        <v>7.59</v>
       </c>
       <c r="N17" t="n">
-        <v>0.788</v>
+        <v>0.466</v>
       </c>
       <c r="O17" t="n">
-        <v>1.464</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45883.07638888889</v>
+        <v>45854.57638888889</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -1507,31 +1507,31 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="L18" t="n">
-        <v>8.01</v>
+        <v>3.72</v>
       </c>
       <c r="M18" t="n">
-        <v>30.71</v>
+        <v>7.59</v>
       </c>
       <c r="N18" t="n">
-        <v>1.039</v>
+        <v>0.466</v>
       </c>
       <c r="O18" t="n">
-        <v>1.525</v>
+        <v>1</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1546,49 +1546,49 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45883.08333333334</v>
+        <v>45854.58333333334</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.061</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K19" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="L19" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M19" t="n">
-        <v>29.99</v>
+        <v>7.59</v>
       </c>
       <c r="N19" t="n">
-        <v>2.129</v>
+        <v>0.466</v>
       </c>
       <c r="O19" t="n">
-        <v>2.586</v>
+        <v>1</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -1603,49 +1603,49 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45883.09027777778</v>
+        <v>45854.59027777778</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.499</v>
+        <v>0.074</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.488</v>
       </c>
       <c r="J20" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K20" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="L20" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M20" t="n">
-        <v>29.99</v>
+        <v>7.59</v>
       </c>
       <c r="N20" t="n">
-        <v>3.628</v>
+        <v>0.54</v>
       </c>
       <c r="O20" t="n">
-        <v>3.586</v>
+        <v>1.488</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1660,49 +1660,49 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45883.09722222222</v>
+        <v>45854.59722222222</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.052</v>
+        <v>0.125</v>
       </c>
       <c r="I21" t="n">
-        <v>0.549</v>
+        <v>0.451</v>
       </c>
       <c r="J21" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K21" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="L21" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M21" t="n">
-        <v>29.28</v>
+        <v>7.59</v>
       </c>
       <c r="N21" t="n">
-        <v>4.68</v>
+        <v>0.665</v>
       </c>
       <c r="O21" t="n">
-        <v>4.135</v>
+        <v>1.939</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1717,49 +1717,49 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45883.10416666666</v>
+        <v>45854.60416666666</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.801</v>
+        <v>0.074</v>
       </c>
       <c r="I22" t="n">
-        <v>0.061</v>
+        <v>0.488</v>
       </c>
       <c r="J22" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K22" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="L22" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M22" t="n">
-        <v>28.57</v>
+        <v>7.59</v>
       </c>
       <c r="N22" t="n">
-        <v>5.481</v>
+        <v>0.739</v>
       </c>
       <c r="O22" t="n">
-        <v>4.196</v>
+        <v>2.427</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45883.11111111111</v>
+        <v>45854.61111111111</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1789,34 +1789,34 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.926</v>
+        <v>0.389</v>
       </c>
       <c r="I23" t="n">
-        <v>0.512</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K23" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="L23" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M23" t="n">
-        <v>28.57</v>
+        <v>7.59</v>
       </c>
       <c r="N23" t="n">
-        <v>6.407</v>
+        <v>1.128</v>
       </c>
       <c r="O23" t="n">
-        <v>4.708</v>
+        <v>2.427</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45883.11805555555</v>
+        <v>45854.61805555555</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1843,37 +1843,37 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.074</v>
+        <v>0.251</v>
       </c>
       <c r="I24" t="n">
-        <v>0.488</v>
+        <v>0.061</v>
       </c>
       <c r="J24" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K24" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="L24" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M24" t="n">
-        <v>28.57</v>
+        <v>7.59</v>
       </c>
       <c r="N24" t="n">
-        <v>6.481</v>
+        <v>1.379</v>
       </c>
       <c r="O24" t="n">
-        <v>5.196</v>
+        <v>2.488</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -1888,16 +1888,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45883.125</v>
+        <v>45854.625</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1909,28 +1909,28 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K25" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="L25" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M25" t="n">
-        <v>27.87</v>
+        <v>7.59</v>
       </c>
       <c r="N25" t="n">
-        <v>6.658</v>
+        <v>1.379</v>
       </c>
       <c r="O25" t="n">
-        <v>5.196</v>
+        <v>2.488</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45883.13194444445</v>
+        <v>45854.63194444445</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1960,34 +1960,34 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.451</v>
       </c>
       <c r="J26" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K26" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="L26" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M26" t="n">
-        <v>27.87</v>
+        <v>7.59</v>
       </c>
       <c r="N26" t="n">
-        <v>6.658</v>
+        <v>1.504</v>
       </c>
       <c r="O26" t="n">
-        <v>5.196</v>
+        <v>2.939</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45883.13888888889</v>
+        <v>45854.63888888889</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2023,28 +2023,28 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="J27" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K27" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="L27" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M27" t="n">
-        <v>27.87</v>
+        <v>7.59</v>
       </c>
       <c r="N27" t="n">
-        <v>6.658</v>
+        <v>1.578</v>
       </c>
       <c r="O27" t="n">
-        <v>5.196</v>
+        <v>3.427</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2059,49 +2059,49 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45883.14583333334</v>
+        <v>45854.64583333334</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.373</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K28" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="L28" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M28" t="n">
-        <v>27.87</v>
+        <v>7.59</v>
       </c>
       <c r="N28" t="n">
-        <v>7.031</v>
+        <v>2.578</v>
       </c>
       <c r="O28" t="n">
-        <v>5.196</v>
+        <v>4.427</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45883.15277777778</v>
+        <v>45854.65277777778</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2128,37 +2128,37 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.251</v>
+        <v>0.611</v>
       </c>
       <c r="I29" t="n">
-        <v>0.061</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K29" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L29" t="n">
-        <v>7.66</v>
+        <v>3.72</v>
       </c>
       <c r="M29" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N29" t="n">
-        <v>7.282</v>
+        <v>3.189</v>
       </c>
       <c r="O29" t="n">
-        <v>5.257</v>
+        <v>5.427</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2173,16 +2173,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45883.15972222222</v>
+        <v>45854.65972222222</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2191,31 +2191,31 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.125</v>
+        <v>0.765</v>
       </c>
       <c r="I30" t="n">
-        <v>0.451</v>
+        <v>0.512</v>
       </c>
       <c r="J30" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="K30" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L30" t="n">
-        <v>7.31</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N30" t="n">
-        <v>7.407</v>
+        <v>3.954</v>
       </c>
       <c r="O30" t="n">
-        <v>5.708</v>
+        <v>5.939</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45883.16666666666</v>
+        <v>45854.66666666666</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2242,37 +2242,37 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.341</v>
+        <v>0.325</v>
       </c>
       <c r="I31" t="n">
-        <v>0.549</v>
+        <v>0.976</v>
       </c>
       <c r="J31" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L31" t="n">
-        <v>7.31</v>
+        <v>3.98</v>
       </c>
       <c r="M31" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N31" t="n">
-        <v>7.748</v>
+        <v>4.279</v>
       </c>
       <c r="O31" t="n">
-        <v>6.257</v>
+        <v>6.915</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45883.17361111111</v>
+        <v>45854.67361111111</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -2302,34 +2302,34 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.534</v>
+        <v>1.035</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="J32" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L32" t="n">
-        <v>7.31</v>
+        <v>4.24</v>
       </c>
       <c r="M32" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N32" t="n">
-        <v>8.282</v>
+        <v>5.314</v>
       </c>
       <c r="O32" t="n">
-        <v>6.257</v>
+        <v>7.878</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -2344,49 +2344,49 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45883.18055555555</v>
+        <v>45854.68055555555</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.074</v>
+        <v>0.839</v>
       </c>
       <c r="I33" t="n">
-        <v>0.488</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="K33" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L33" t="n">
-        <v>7.31</v>
+        <v>4.52</v>
       </c>
       <c r="M33" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N33" t="n">
-        <v>8.356</v>
+        <v>6.153</v>
       </c>
       <c r="O33" t="n">
-        <v>6.745</v>
+        <v>8.878</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -2401,49 +2401,49 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45883.1875</v>
+        <v>45854.6875</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.376</v>
+        <v>1.074</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.488</v>
       </c>
       <c r="J34" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="K34" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="L34" t="n">
-        <v>7.66</v>
+        <v>5.09</v>
       </c>
       <c r="M34" t="n">
-        <v>27.18</v>
+        <v>7.59</v>
       </c>
       <c r="N34" t="n">
-        <v>8.731999999999999</v>
+        <v>7.227</v>
       </c>
       <c r="O34" t="n">
-        <v>7.684</v>
+        <v>10.366</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -2458,49 +2458,49 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45883.19444444445</v>
+        <v>45854.69444444445</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0.325</v>
+        <v>1.251</v>
       </c>
       <c r="I35" t="n">
-        <v>0.549</v>
+        <v>1.061</v>
       </c>
       <c r="J35" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="K35" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="L35" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="M35" t="n">
         <v>8.01</v>
       </c>
-      <c r="M35" t="n">
-        <v>27.18</v>
-      </c>
       <c r="N35" t="n">
-        <v>9.057</v>
+        <v>8.478</v>
       </c>
       <c r="O35" t="n">
-        <v>8.233000000000001</v>
+        <v>11.427</v>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -2515,49 +2515,49 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883.20138888889</v>
+        <v>45854.70138888889</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.373</v>
+        <v>1.016</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="K36" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="L36" t="n">
-        <v>8.369999999999999</v>
+        <v>6.64</v>
       </c>
       <c r="M36" t="n">
-        <v>27.18</v>
+        <v>8.01</v>
       </c>
       <c r="N36" t="n">
-        <v>9.43</v>
+        <v>9.494</v>
       </c>
       <c r="O36" t="n">
-        <v>8.233000000000001</v>
+        <v>12.427</v>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -2572,49 +2572,49 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45883.20833333334</v>
+        <v>45854.70833333334</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.23</v>
+        <v>0.608</v>
       </c>
       <c r="I37" t="n">
-        <v>1.952</v>
+        <v>0.488</v>
       </c>
       <c r="J37" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="K37" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="L37" t="n">
-        <v>8.73</v>
+        <v>7.31</v>
       </c>
       <c r="M37" t="n">
-        <v>27.18</v>
+        <v>8.44</v>
       </c>
       <c r="N37" t="n">
-        <v>11.66</v>
+        <v>10.102</v>
       </c>
       <c r="O37" t="n">
-        <v>10.185</v>
+        <v>12.915</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -2629,55 +2629,55 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883.21527777778</v>
+        <v>45854.71527777778</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.837</v>
+        <v>0.392</v>
       </c>
       <c r="I38" t="n">
-        <v>0.61</v>
+        <v>0.512</v>
       </c>
       <c r="J38" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K38" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="L38" t="n">
-        <v>9.109999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="M38" t="n">
-        <v>26.49</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>13.497</v>
+        <v>10.494</v>
       </c>
       <c r="O38" t="n">
-        <v>10.795</v>
+        <v>13.427</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9336103796958923</v>
+        <v>0.9942529797554016</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.098110675811768</v>
+        <v>1.976800322532654</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2690,55 +2690,55 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45883.22222222222</v>
+        <v>45854.72222222222</v>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>6.965</v>
+        <v>0.91</v>
       </c>
       <c r="I39" t="n">
-        <v>3.109</v>
+        <v>0.512</v>
       </c>
       <c r="J39" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="L39" t="n">
-        <v>9.48</v>
+        <v>10.66</v>
       </c>
       <c r="M39" t="n">
-        <v>26.49</v>
+        <v>9.33</v>
       </c>
       <c r="N39" t="n">
-        <v>20.462</v>
+        <v>11.404</v>
       </c>
       <c r="O39" t="n">
-        <v>13.904</v>
+        <v>13.939</v>
       </c>
       <c r="P39" t="n">
-        <v>0.9565637111663818</v>
+        <v>1.004305839538574</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.109521150588989</v>
+        <v>2.014098644256592</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2751,55 +2751,55 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45883.22916666666</v>
+        <v>45854.72916666666</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1.359</v>
+        <v>0.875</v>
       </c>
       <c r="I40" t="n">
-        <v>2.817</v>
+        <v>0.549</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="K40" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="L40" t="n">
-        <v>10.66</v>
+        <v>13.61</v>
       </c>
       <c r="M40" t="n">
-        <v>26.49</v>
+        <v>9.33</v>
       </c>
       <c r="N40" t="n">
-        <v>21.821</v>
+        <v>12.279</v>
       </c>
       <c r="O40" t="n">
-        <v>16.721</v>
+        <v>14.488</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9813870787620544</v>
+        <v>1.019075870513916</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.155590295791626</v>
+        <v>2.050552606582642</v>
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2812,55 +2812,55 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45883.23611111111</v>
+        <v>45854.73611111111</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1.391</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>4.961</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="K41" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="L41" t="n">
-        <v>15.43</v>
+        <v>16.38</v>
       </c>
       <c r="M41" t="n">
-        <v>27.18</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>23.212</v>
+        <v>13.279</v>
       </c>
       <c r="O41" t="n">
-        <v>21.682</v>
+        <v>15.488</v>
       </c>
       <c r="P41" t="n">
-        <v>1.030472159385681</v>
+        <v>1.02919602394104</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.282051801681519</v>
+        <v>2.082365274429321</v>
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2873,55 +2873,55 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45883.24305555555</v>
+        <v>45854.74305555555</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
         <v>3</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
-        <v>0.375</v>
+        <v>2.052</v>
       </c>
       <c r="I42" t="n">
-        <v>1.353</v>
+        <v>1.122</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="K42" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="L42" t="n">
-        <v>19.88</v>
+        <v>18.35</v>
       </c>
       <c r="M42" t="n">
-        <v>27.87</v>
+        <v>10.73</v>
       </c>
       <c r="N42" t="n">
-        <v>23.587</v>
+        <v>15.331</v>
       </c>
       <c r="O42" t="n">
-        <v>23.035</v>
+        <v>16.61</v>
       </c>
       <c r="P42" t="n">
-        <v>1.124661922454834</v>
+        <v>1.03579843044281</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.387581348419189</v>
+        <v>2.119031190872192</v>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2934,55 +2934,55 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45883.25</v>
+        <v>45854.75</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.25</v>
+        <v>1.376</v>
       </c>
       <c r="I43" t="n">
-        <v>0.902</v>
+        <v>1.939</v>
       </c>
       <c r="J43" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="K43" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="L43" t="n">
-        <v>20.94</v>
+        <v>19.88</v>
       </c>
       <c r="M43" t="n">
-        <v>29.28</v>
+        <v>11.21</v>
       </c>
       <c r="N43" t="n">
-        <v>23.837</v>
+        <v>16.707</v>
       </c>
       <c r="O43" t="n">
-        <v>23.937</v>
+        <v>18.549</v>
       </c>
       <c r="P43" t="n">
-        <v>1.255199193954468</v>
+        <v>1.044118285179138</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.422261714935303</v>
+        <v>2.150784492492676</v>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -2995,55 +2995,55 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45883.25694444445</v>
+        <v>45854.75694444445</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>4</v>
-      </c>
       <c r="H44" t="n">
-        <v>1.277</v>
+        <v>1.812</v>
       </c>
       <c r="I44" t="n">
-        <v>1.671</v>
+        <v>4.329</v>
       </c>
       <c r="J44" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="K44" t="n">
-        <v>2.86</v>
+        <v>1.91</v>
       </c>
       <c r="L44" t="n">
-        <v>22.01</v>
+        <v>21.47</v>
       </c>
       <c r="M44" t="n">
-        <v>104.86</v>
+        <v>12.71</v>
       </c>
       <c r="N44" t="n">
-        <v>25.114</v>
+        <v>18.519</v>
       </c>
       <c r="O44" t="n">
-        <v>25.608</v>
+        <v>22.878</v>
       </c>
       <c r="P44" t="n">
-        <v>1.357344388961792</v>
+        <v>1.065097212791443</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.455896615982056</v>
+        <v>2.204257488250732</v>
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3056,55 +3056,55 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45883.26388888889</v>
+        <v>45854.76388888889</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
         <v>4</v>
       </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
-        <v>1.649</v>
+        <v>3.662</v>
       </c>
       <c r="I45" t="n">
-        <v>0.451</v>
+        <v>3.963</v>
       </c>
       <c r="J45" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="K45" t="n">
-        <v>2.93</v>
+        <v>1.94</v>
       </c>
       <c r="L45" t="n">
-        <v>27.61</v>
+        <v>24.8</v>
       </c>
       <c r="M45" t="n">
-        <v>114.92</v>
+        <v>14.28</v>
       </c>
       <c r="N45" t="n">
-        <v>26.763</v>
+        <v>22.181</v>
       </c>
       <c r="O45" t="n">
-        <v>26.059</v>
+        <v>26.841</v>
       </c>
       <c r="P45" t="n">
-        <v>1.418434262275696</v>
+        <v>1.097640156745911</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.477810382843018</v>
+        <v>2.242937326431274</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45883.27083333334</v>
+        <v>45854.77083333334</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
@@ -3129,43 +3129,43 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>1.103</v>
+        <v>3.038</v>
       </c>
       <c r="I46" t="n">
-        <v>0.549</v>
+        <v>3.475</v>
       </c>
       <c r="J46" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="K46" t="n">
-        <v>2.91</v>
+        <v>1.98</v>
       </c>
       <c r="L46" t="n">
-        <v>31.11</v>
+        <v>30.51</v>
       </c>
       <c r="M46" t="n">
-        <v>112.01</v>
+        <v>16.48</v>
       </c>
       <c r="N46" t="n">
-        <v>27.866</v>
+        <v>25.219</v>
       </c>
       <c r="O46" t="n">
-        <v>26.608</v>
+        <v>30.316</v>
       </c>
       <c r="P46" t="n">
-        <v>1.468310475349426</v>
+        <v>1.188491225242615</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.522948265075684</v>
+        <v>2.273525714874268</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3178,55 +3178,55 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45883.27777777778</v>
+        <v>45854.77777777778</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
-        <v>0.286</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>0.451</v>
+        <v>3.634</v>
       </c>
       <c r="J47" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="K47" t="n">
-        <v>2.86</v>
+        <v>2.02</v>
       </c>
       <c r="L47" t="n">
-        <v>31.11</v>
+        <v>33.6</v>
       </c>
       <c r="M47" t="n">
-        <v>104.86</v>
+        <v>18.81</v>
       </c>
       <c r="N47" t="n">
-        <v>28.152</v>
+        <v>29.419</v>
       </c>
       <c r="O47" t="n">
-        <v>27.059</v>
+        <v>33.95</v>
       </c>
       <c r="P47" t="n">
-        <v>1.49199104309082</v>
+        <v>1.284444570541382</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.603324413299561</v>
+        <v>2.327766418457031</v>
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3239,55 +3239,55 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45883.28472222222</v>
+        <v>45854.78472222222</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>0.649</v>
+        <v>3.511</v>
       </c>
       <c r="I48" t="n">
-        <v>1.939</v>
+        <v>5.464</v>
       </c>
       <c r="J48" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="K48" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="L48" t="n">
-        <v>32.34</v>
+        <v>41.05</v>
       </c>
       <c r="M48" t="n">
-        <v>102.04</v>
+        <v>22.52</v>
       </c>
       <c r="N48" t="n">
-        <v>28.801</v>
+        <v>32.93</v>
       </c>
       <c r="O48" t="n">
-        <v>28.998</v>
+        <v>39.414</v>
       </c>
       <c r="P48" t="n">
-        <v>1.502994060516357</v>
+        <v>1.391403198242188</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.695004463195801</v>
+        <v>2.394465208053589</v>
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3300,55 +3300,55 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45883.29166666666</v>
+        <v>45854.79166666666</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>0.591</v>
+        <v>3.358</v>
       </c>
       <c r="I49" t="n">
-        <v>1.451</v>
+        <v>2.159</v>
       </c>
       <c r="J49" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="K49" t="n">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="L49" t="n">
-        <v>35.54</v>
+        <v>59.76</v>
       </c>
       <c r="M49" t="n">
-        <v>104.86</v>
+        <v>25.81</v>
       </c>
       <c r="N49" t="n">
-        <v>29.392</v>
+        <v>36.288</v>
       </c>
       <c r="O49" t="n">
-        <v>30.449</v>
+        <v>41.573</v>
       </c>
       <c r="P49" t="n">
-        <v>1.497017979621887</v>
+        <v>1.49540901184082</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.755085468292236</v>
+        <v>2.496608257293701</v>
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3361,55 +3361,55 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45883.29861111111</v>
+        <v>45854.79861111111</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>1.574</v>
+        <v>3.956</v>
       </c>
       <c r="I50" t="n">
-        <v>2.865</v>
+        <v>2.159</v>
       </c>
       <c r="J50" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="K50" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="L50" t="n">
-        <v>38.23</v>
+        <v>76.5</v>
       </c>
       <c r="M50" t="n">
-        <v>107.7</v>
+        <v>36.72</v>
       </c>
       <c r="N50" t="n">
-        <v>30.966</v>
+        <v>40.244</v>
       </c>
       <c r="O50" t="n">
-        <v>33.314</v>
+        <v>43.732</v>
       </c>
       <c r="P50" t="n">
-        <v>1.500973463058472</v>
+        <v>1.603531241416931</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.79084038734436</v>
+        <v>2.600229263305664</v>
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3422,55 +3422,55 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45883.30555555555</v>
+        <v>45854.80555555555</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>1.708</v>
+        <v>2.728</v>
       </c>
       <c r="I51" t="n">
-        <v>0.061</v>
+        <v>0.732</v>
       </c>
       <c r="J51" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="K51" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="L51" t="n">
-        <v>38.23</v>
+        <v>83.03</v>
       </c>
       <c r="M51" t="n">
-        <v>109.13</v>
+        <v>112.01</v>
       </c>
       <c r="N51" t="n">
-        <v>32.674</v>
+        <v>42.972</v>
       </c>
       <c r="O51" t="n">
-        <v>33.375</v>
+        <v>44.464</v>
       </c>
       <c r="P51" t="n">
-        <v>1.511009454727173</v>
+        <v>1.684550881385803</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.820606231689453</v>
+        <v>2.749763250350952</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3483,55 +3483,55 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45883.3125</v>
+        <v>45854.8125</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="n">
         <v>3</v>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>0.582</v>
+        <v>3.422</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2.037</v>
       </c>
       <c r="J52" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="K52" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="L52" t="n">
-        <v>37.55</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>106.28</v>
+        <v>143.74</v>
       </c>
       <c r="N52" t="n">
-        <v>33.256</v>
+        <v>46.394</v>
       </c>
       <c r="O52" t="n">
-        <v>33.375</v>
+        <v>46.501</v>
       </c>
       <c r="P52" t="n">
-        <v>1.546143889427185</v>
+        <v>1.723007798194885</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.836099863052368</v>
+        <v>2.933917760848999</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3544,16 +3544,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45883.31944444445</v>
+        <v>45854.81944444445</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -3562,37 +3562,37 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>0.486</v>
+        <v>2.937</v>
       </c>
       <c r="I53" t="n">
-        <v>0.549</v>
+        <v>0.61</v>
       </c>
       <c r="J53" t="n">
-        <v>1.48</v>
+        <v>2.03</v>
       </c>
       <c r="K53" t="n">
-        <v>2.85</v>
+        <v>3.33</v>
       </c>
       <c r="L53" t="n">
-        <v>36.2</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>103.45</v>
+        <v>177.13</v>
       </c>
       <c r="N53" t="n">
-        <v>33.742</v>
+        <v>49.331</v>
       </c>
       <c r="O53" t="n">
-        <v>33.924</v>
+        <v>47.111</v>
       </c>
       <c r="P53" t="n">
-        <v>1.54832136631012</v>
+        <v>1.751156806945801</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.885217666625977</v>
+        <v>3.131009101867676</v>
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3605,55 +3605,55 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45883.32638888889</v>
+        <v>45854.82638888889</v>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.316</v>
+        <v>1.489</v>
       </c>
       <c r="I54" t="n">
-        <v>0.512</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="K54" t="n">
-        <v>2.84</v>
+        <v>3.52</v>
       </c>
       <c r="L54" t="n">
-        <v>38.23</v>
+        <v>78.64</v>
       </c>
       <c r="M54" t="n">
-        <v>102.04</v>
+        <v>209.45</v>
       </c>
       <c r="N54" t="n">
-        <v>36.058</v>
+        <v>50.82</v>
       </c>
       <c r="O54" t="n">
-        <v>34.436</v>
+        <v>47.111</v>
       </c>
       <c r="P54" t="n">
-        <v>1.53042733669281</v>
+        <v>1.764213442802429</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.933662414550781</v>
+        <v>3.315243721008301</v>
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3666,55 +3666,55 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45883.33333333334</v>
+        <v>45854.83333333334</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6.852</v>
+        <v>0.447</v>
       </c>
       <c r="I55" t="n">
-        <v>2.647</v>
+        <v>0.488</v>
       </c>
       <c r="J55" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="K55" t="n">
-        <v>2.85</v>
+        <v>3.66</v>
       </c>
       <c r="L55" t="n">
-        <v>42.51</v>
+        <v>69.3</v>
       </c>
       <c r="M55" t="n">
-        <v>103.45</v>
+        <v>234.61</v>
       </c>
       <c r="N55" t="n">
-        <v>42.91</v>
+        <v>51.267</v>
       </c>
       <c r="O55" t="n">
-        <v>37.083</v>
+        <v>47.599</v>
       </c>
       <c r="P55" t="n">
-        <v>1.52211594581604</v>
+        <v>1.741832375526428</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.977582693099976</v>
+        <v>3.474599599838257</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3727,55 +3727,55 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45883.34027777778</v>
+        <v>45854.84027777778</v>
       </c>
       <c r="B56" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>15.135</v>
+        <v>1.19</v>
       </c>
       <c r="I56" t="n">
-        <v>9.148</v>
+        <v>0.061</v>
       </c>
       <c r="J56" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="K56" t="n">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="L56" t="n">
-        <v>42.51</v>
+        <v>60.68</v>
       </c>
       <c r="M56" t="n">
-        <v>120.8</v>
+        <v>251.39</v>
       </c>
       <c r="N56" t="n">
-        <v>58.045</v>
+        <v>52.457</v>
       </c>
       <c r="O56" t="n">
-        <v>46.231</v>
+        <v>47.66</v>
       </c>
       <c r="P56" t="n">
-        <v>1.477759122848511</v>
+        <v>1.702126264572144</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.010376691818237</v>
+        <v>3.579947710037231</v>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3788,55 +3788,55 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45883.34722222222</v>
+        <v>45854.84722222222</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>4.382</v>
+        <v>0.463</v>
       </c>
       <c r="I57" t="n">
-        <v>6.584</v>
+        <v>0.451</v>
       </c>
       <c r="J57" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="K57" t="n">
-        <v>3.25</v>
+        <v>3.79</v>
       </c>
       <c r="L57" t="n">
-        <v>49.46</v>
+        <v>52.76</v>
       </c>
       <c r="M57" t="n">
-        <v>164.18</v>
+        <v>258.99</v>
       </c>
       <c r="N57" t="n">
-        <v>62.427</v>
+        <v>52.92</v>
       </c>
       <c r="O57" t="n">
-        <v>52.815</v>
+        <v>48.111</v>
       </c>
       <c r="P57" t="n">
-        <v>1.476979494094849</v>
+        <v>1.666799187660217</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.157265901565552</v>
+        <v>3.638675212860107</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -3849,13 +3849,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45883.35416666666</v>
+        <v>45854.85416666666</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -3864,40 +3864,40 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.498</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0.451</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="K58" t="n">
-        <v>3.53</v>
+        <v>3.76</v>
       </c>
       <c r="L58" t="n">
-        <v>56.19</v>
+        <v>45.52</v>
       </c>
       <c r="M58" t="n">
-        <v>211.21</v>
+        <v>253.28</v>
       </c>
       <c r="N58" t="n">
-        <v>62.925</v>
+        <v>52.92</v>
       </c>
       <c r="O58" t="n">
-        <v>53.266</v>
+        <v>48.111</v>
       </c>
       <c r="P58" t="n">
-        <v>1.554173827171326</v>
+        <v>1.631922602653503</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.571202039718628</v>
+        <v>3.668315649032593</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45883.36111111111</v>
+        <v>45854.86111111111</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -3922,43 +3922,43 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.125</v>
+        <v>1.477</v>
       </c>
       <c r="I59" t="n">
-        <v>0.451</v>
+        <v>1.769</v>
       </c>
       <c r="J59" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="K59" t="n">
-        <v>3.84</v>
+        <v>3.69</v>
       </c>
       <c r="L59" t="n">
-        <v>57.96</v>
+        <v>40.34</v>
       </c>
       <c r="M59" t="n">
-        <v>268.62</v>
+        <v>240.16</v>
       </c>
       <c r="N59" t="n">
-        <v>63.05</v>
+        <v>54.397</v>
       </c>
       <c r="O59" t="n">
-        <v>53.717</v>
+        <v>49.88</v>
       </c>
       <c r="P59" t="n">
-        <v>1.697535395622253</v>
+        <v>1.586693406105042</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.796570777893066</v>
+        <v>3.644210815429688</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -3971,55 +3971,55 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45883.36805555555</v>
+        <v>45854.86805555555</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2.068</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="J60" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="K60" t="n">
-        <v>4.01</v>
+        <v>3.59</v>
       </c>
       <c r="L60" t="n">
-        <v>63.47</v>
+        <v>36.2</v>
       </c>
       <c r="M60" t="n">
-        <v>302.4</v>
+        <v>221.89</v>
       </c>
       <c r="N60" t="n">
-        <v>63.05</v>
+        <v>56.465</v>
       </c>
       <c r="O60" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P60" t="n">
-        <v>1.798274993896484</v>
+        <v>1.530776739120483</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.930526733398438</v>
+        <v>3.585196971893311</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45883.375</v>
+        <v>45854.875</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -4053,34 +4053,34 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="K61" t="n">
-        <v>4.06</v>
+        <v>3.47</v>
       </c>
       <c r="L61" t="n">
-        <v>74.40000000000001</v>
+        <v>32.97</v>
       </c>
       <c r="M61" t="n">
-        <v>312.64</v>
+        <v>200.73</v>
       </c>
       <c r="N61" t="n">
-        <v>63.05</v>
+        <v>56.481</v>
       </c>
       <c r="O61" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P61" t="n">
-        <v>1.854300618171692</v>
+        <v>1.496519565582275</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.995487213134766</v>
+        <v>3.517205476760864</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45883.38194444445</v>
+        <v>45854.88194444445</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -4114,34 +4114,34 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>2.01</v>
+        <v>1.39</v>
       </c>
       <c r="K62" t="n">
-        <v>4.06</v>
+        <v>3.36</v>
       </c>
       <c r="L62" t="n">
-        <v>83.03</v>
+        <v>30.51</v>
       </c>
       <c r="M62" t="n">
-        <v>312.64</v>
+        <v>182.09</v>
       </c>
       <c r="N62" t="n">
-        <v>63.05</v>
+        <v>56.642</v>
       </c>
       <c r="O62" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P62" t="n">
-        <v>1.870014667510986</v>
+        <v>1.471284151077271</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.0186448097229</v>
+        <v>3.460820436477661</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45883.38888888889</v>
+        <v>45854.88888888889</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -4181,28 +4181,28 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="K63" t="n">
-        <v>4.02</v>
+        <v>3.26</v>
       </c>
       <c r="L63" t="n">
-        <v>83.03</v>
+        <v>28.75</v>
       </c>
       <c r="M63" t="n">
-        <v>304.44</v>
+        <v>165.78</v>
       </c>
       <c r="N63" t="n">
-        <v>63.05</v>
+        <v>56.642</v>
       </c>
       <c r="O63" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P63" t="n">
-        <v>1.856998443603516</v>
+        <v>1.447106719017029</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.010915756225586</v>
+        <v>3.399074554443359</v>
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -4215,13 +4215,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45883.39583333334</v>
+        <v>45854.89583333334</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -4236,34 +4236,34 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="K64" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="L64" t="n">
-        <v>71.31</v>
+        <v>26.5</v>
       </c>
       <c r="M64" t="n">
-        <v>290.3</v>
+        <v>153.17</v>
       </c>
       <c r="N64" t="n">
-        <v>63.05</v>
+        <v>57.015</v>
       </c>
       <c r="O64" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P64" t="n">
-        <v>1.824661254882812</v>
+        <v>1.413847804069519</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.97983717918396</v>
+        <v>3.323092937469482</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45883.40277777778</v>
+        <v>45854.90277777778</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -4303,28 +4303,28 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="K65" t="n">
-        <v>3.85</v>
+        <v>3.11</v>
       </c>
       <c r="L65" t="n">
-        <v>60.68</v>
+        <v>24.8</v>
       </c>
       <c r="M65" t="n">
-        <v>270.56</v>
+        <v>142.17</v>
       </c>
       <c r="N65" t="n">
-        <v>63.05</v>
+        <v>57.015</v>
       </c>
       <c r="O65" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P65" t="n">
-        <v>1.780310153961182</v>
+        <v>1.381854176521301</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.930671453475952</v>
+        <v>3.243587493896484</v>
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45883.40972222222</v>
+        <v>45854.90972222222</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -4364,28 +4364,28 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="K66" t="n">
-        <v>3.72</v>
+        <v>3.04</v>
       </c>
       <c r="L66" t="n">
-        <v>51.09</v>
+        <v>22.56</v>
       </c>
       <c r="M66" t="n">
-        <v>245.75</v>
+        <v>131.34</v>
       </c>
       <c r="N66" t="n">
-        <v>63.05</v>
+        <v>57.015</v>
       </c>
       <c r="O66" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P66" t="n">
-        <v>1.729285717010498</v>
+        <v>1.351646661758423</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.867480516433716</v>
+        <v>3.163244009017944</v>
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45883.41666666666</v>
+        <v>45854.91666666666</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -4419,34 +4419,34 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="K67" t="n">
-        <v>3.59</v>
+        <v>2.98</v>
       </c>
       <c r="L67" t="n">
-        <v>44.75</v>
+        <v>21.47</v>
       </c>
       <c r="M67" t="n">
-        <v>221.89</v>
+        <v>122.29</v>
       </c>
       <c r="N67" t="n">
-        <v>63.05</v>
+        <v>57.031</v>
       </c>
       <c r="O67" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P67" t="n">
-        <v>1.675752639770508</v>
+        <v>1.32326865196228</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.793836832046509</v>
+        <v>3.080927610397339</v>
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4459,7 +4459,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45883.42361111111</v>
+        <v>45854.92361111111</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -4486,28 +4486,28 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="K68" t="n">
-        <v>3.47</v>
+        <v>2.92</v>
       </c>
       <c r="L68" t="n">
-        <v>41.05</v>
+        <v>19.88</v>
       </c>
       <c r="M68" t="n">
-        <v>200.73</v>
+        <v>113.46</v>
       </c>
       <c r="N68" t="n">
-        <v>63.05</v>
+        <v>57.031</v>
       </c>
       <c r="O68" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P68" t="n">
-        <v>1.622387647628784</v>
+        <v>1.297042369842529</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.712075233459473</v>
+        <v>3.000465393066406</v>
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45883.43055555555</v>
+        <v>45854.93055555555</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -4547,28 +4547,28 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="K69" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="L69" t="n">
-        <v>39.63</v>
+        <v>18.85</v>
       </c>
       <c r="M69" t="n">
-        <v>183.76</v>
+        <v>103.45</v>
       </c>
       <c r="N69" t="n">
-        <v>63.05</v>
+        <v>57.031</v>
       </c>
       <c r="O69" t="n">
-        <v>53.717</v>
+        <v>50.49</v>
       </c>
       <c r="P69" t="n">
-        <v>1.571199417114258</v>
+        <v>1.273271560668945</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.624535322189331</v>
+        <v>2.923388719558716</v>
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45883.4375</v>
+        <v>45854.9375</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -4593,43 +4593,43 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.251</v>
+        <v>0.45</v>
       </c>
       <c r="I70" t="n">
-        <v>0.061</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="K70" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="L70" t="n">
-        <v>37.55</v>
+        <v>17.85</v>
       </c>
       <c r="M70" t="n">
-        <v>168.99</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>63.301</v>
+        <v>57.481</v>
       </c>
       <c r="O70" t="n">
-        <v>53.778</v>
+        <v>51.49</v>
       </c>
       <c r="P70" t="n">
-        <v>1.523335576057434</v>
+        <v>1.251830577850342</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.534058094024658</v>
+        <v>2.848945379257202</v>
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4642,19 +4642,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45883.44444444445</v>
+        <v>45854.94444444445</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -4663,34 +4663,34 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.572</v>
+        <v>0.125</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="J71" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="K71" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="L71" t="n">
-        <v>34.88</v>
+        <v>16.86</v>
       </c>
       <c r="M71" t="n">
-        <v>156.28</v>
+        <v>92.39</v>
       </c>
       <c r="N71" t="n">
-        <v>63.873</v>
+        <v>57.606</v>
       </c>
       <c r="O71" t="n">
-        <v>54.717</v>
+        <v>51.941</v>
       </c>
       <c r="P71" t="n">
-        <v>1.476534366607666</v>
+        <v>1.232574462890625</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.441529989242554</v>
+        <v>2.776635885238647</v>
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -4703,16 +4703,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45883.45138888889</v>
+        <v>45854.95138888889</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -4724,34 +4724,34 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.177</v>
+        <v>0.373</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="K72" t="n">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="L72" t="n">
-        <v>32.97</v>
+        <v>15.9</v>
       </c>
       <c r="M72" t="n">
-        <v>142.17</v>
+        <v>89.69</v>
       </c>
       <c r="N72" t="n">
-        <v>64.05</v>
+        <v>57.979</v>
       </c>
       <c r="O72" t="n">
-        <v>54.717</v>
+        <v>51.941</v>
       </c>
       <c r="P72" t="n">
-        <v>1.44068717956543</v>
+        <v>1.229535818099976</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.354008197784424</v>
+        <v>2.707565546035767</v>
       </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45883.45833333334</v>
+        <v>45854.95833333334</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -4785,34 +4785,34 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K73" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="L73" t="n">
-        <v>31.11</v>
+        <v>14.97</v>
       </c>
       <c r="M73" t="n">
-        <v>131.34</v>
+        <v>85.7</v>
       </c>
       <c r="N73" t="n">
-        <v>64.066</v>
+        <v>57.979</v>
       </c>
       <c r="O73" t="n">
-        <v>54.717</v>
+        <v>51.941</v>
       </c>
       <c r="P73" t="n">
-        <v>1.421925663948059</v>
+        <v>1.229290723800659</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.268915414810181</v>
+        <v>2.645242214202881</v>
       </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
